--- a/DiagnosticReportIG/CurrentBuild/all-profiles.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:17:39+00:00</t>
+    <t>2026-08-31T14:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1391,7 +1391,7 @@
     <t>History</t>
   </si>
   <si>
-    <t>Indicates if an observation (or possibly awhole report) is 'history', i.e. a copy/repetition af information sent previously.</t>
+    <t>Indicates if an observation (or possibly a whole report) is 'history', i.e. a copy/repetition of information sent previously.</t>
   </si>
   <si>
     <t>nilar-inf-item-coded-descr</t>
